--- a/russian_data/processed/DATASET-industries.xlsx
+++ b/russian_data/processed/DATASET-industries.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -421,69 +433,69 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>ret_t</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rpo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rea_t</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>delta_world</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>delta_non_rus</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>BRENT</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>cpi_us</t>
+          <t>cpi_rus</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>log_real_brent</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>consumer_log_return</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>metals_mining_log_return</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>oil_gas_log_return</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38353</v>
       </c>
       <c r="B2" t="n">
@@ -505,10 +517,10 @@
         <v>39.64428571429</v>
       </c>
       <c r="H2" t="n">
-        <v>191.6</v>
+        <v>57.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.575463046018722</v>
+        <v>-0.3666070788677143</v>
       </c>
       <c r="J2" t="n">
         <v>0.0519565743687415</v>
@@ -521,7 +533,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38384</v>
       </c>
       <c r="B3" t="n">
@@ -543,10 +555,10 @@
         <v>44.28333333333</v>
       </c>
       <c r="H3" t="n">
-        <v>192.4</v>
+        <v>58.7</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.468968154693969</v>
+        <v>-0.2818313432964135</v>
       </c>
       <c r="J3" t="n">
         <v>0.2155942167860498</v>
@@ -559,7 +571,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38412</v>
       </c>
       <c r="B4" t="n">
@@ -581,10 +593,10 @@
         <v>45.557</v>
       </c>
       <c r="H4" t="n">
-        <v>193.1</v>
+        <v>59.42</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.444243900257927</v>
+        <v>-0.2656665808579208</v>
       </c>
       <c r="J4" t="n">
         <v>0.0482667409698347</v>
@@ -597,7 +609,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38443</v>
       </c>
       <c r="B5" t="n">
@@ -619,10 +631,10 @@
         <v>53.08409090909</v>
       </c>
       <c r="H5" t="n">
-        <v>193.7</v>
+        <v>60.22</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.294433293287798</v>
+        <v>-0.1261272459284348</v>
       </c>
       <c r="J5" t="n">
         <v>-0.0357040291727974</v>
@@ -635,7 +647,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38473</v>
       </c>
       <c r="B6" t="n">
@@ -657,10 +669,10 @@
         <v>51.85714285714</v>
       </c>
       <c r="H6" t="n">
-        <v>193.6</v>
+        <v>60.89</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.317301489632995</v>
+        <v>-0.1605762724110007</v>
       </c>
       <c r="J6" t="n">
         <v>0.1713696766565284</v>
@@ -673,7 +685,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38504</v>
       </c>
       <c r="B7" t="n">
@@ -695,10 +707,10 @@
         <v>48.66590909091</v>
       </c>
       <c r="H7" t="n">
-        <v>193.7</v>
+        <v>61.38</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.381331804119022</v>
+        <v>-0.232105282897662</v>
       </c>
       <c r="J7" t="n">
         <v>0.0528071354727108</v>
@@ -711,7 +723,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38534</v>
       </c>
       <c r="B8" t="n">
@@ -733,10 +745,10 @@
         <v>54.30681818182</v>
       </c>
       <c r="H8" t="n">
-        <v>194.9</v>
+        <v>61.77</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.277836822413529</v>
+        <v>-0.128768025607823</v>
       </c>
       <c r="J8" t="n">
         <v>0.0250606500103378</v>
@@ -749,7 +761,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38565</v>
       </c>
       <c r="B9" t="n">
@@ -771,10 +783,10 @@
         <v>57.57904761905</v>
       </c>
       <c r="H9" t="n">
-        <v>196.1</v>
+        <v>62.06</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.225465988289655</v>
+        <v>-0.0749429141075888</v>
       </c>
       <c r="J9" t="n">
         <v>0.1829564796309455</v>
@@ -787,7 +799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38596</v>
       </c>
       <c r="B10" t="n">
@@ -809,10 +821,10 @@
         <v>64.09</v>
       </c>
       <c r="H10" t="n">
-        <v>198.8</v>
+        <v>61.97</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.132010948706339</v>
+        <v>0.03363794854211921</v>
       </c>
       <c r="J10" t="n">
         <v>0.1121530453335148</v>
@@ -825,7 +837,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>38626</v>
       </c>
       <c r="B11" t="n">
@@ -847,10 +859,10 @@
         <v>62.98181818182</v>
       </c>
       <c r="H11" t="n">
-        <v>199.1</v>
+        <v>62.12</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.150961126620267</v>
+        <v>0.01377808616939813</v>
       </c>
       <c r="J11" t="n">
         <v>-0.0441681914500247</v>
@@ -863,7 +875,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>38657</v>
       </c>
       <c r="B12" t="n">
@@ -885,10 +897,10 @@
         <v>58.5219047619</v>
       </c>
       <c r="H12" t="n">
-        <v>198.1</v>
+        <v>62.47</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.219370829177638</v>
+        <v>-0.06528531697861162</v>
       </c>
       <c r="J12" t="n">
         <v>0.1030040561921943</v>
@@ -901,7 +913,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>38687</v>
       </c>
       <c r="B13" t="n">
@@ -923,10 +935,10 @@
         <v>55.535</v>
       </c>
       <c r="H13" t="n">
-        <v>198.1</v>
+        <v>62.93</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.271758501085422</v>
+        <v>-0.1250095449197595</v>
       </c>
       <c r="J13" t="n">
         <v>-0.0002232705842004</v>
@@ -939,7 +951,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>38718</v>
       </c>
       <c r="B14" t="n">
@@ -961,10 +973,10 @@
         <v>56.7475</v>
       </c>
       <c r="H14" t="n">
-        <v>199.3</v>
+        <v>63.44</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.256199624691029</v>
+        <v>-0.1114829747988733</v>
       </c>
       <c r="J14" t="n">
         <v>0.0764763509928405</v>
@@ -977,7 +989,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>38749</v>
       </c>
       <c r="B15" t="n">
@@ -999,10 +1011,10 @@
         <v>63.57428571429</v>
       </c>
       <c r="H15" t="n">
-        <v>199.4</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.143103781606462</v>
+        <v>-0.0220243359849821</v>
       </c>
       <c r="J15" t="n">
         <v>0.0159569263204941</v>
@@ -1015,7 +1027,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>38777</v>
       </c>
       <c r="B16" t="n">
@@ -1037,10 +1049,10 @@
         <v>59.923</v>
       </c>
       <c r="H16" t="n">
-        <v>199.7</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.203755835710429</v>
+        <v>-0.09765438133045379</v>
       </c>
       <c r="J16" t="n">
         <v>0.0296227440279679</v>
@@ -1053,11 +1065,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>38808</v>
       </c>
       <c r="B17" t="n">
-        <v>12.67788644118132</v>
+        <v>12.67788644118133</v>
       </c>
       <c r="C17" t="n">
         <v>3.43708444913175</v>
@@ -1075,10 +1087,10 @@
         <v>62.25304347826</v>
       </c>
       <c r="H17" t="n">
-        <v>200.7</v>
+        <v>66.61</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.170603830435583</v>
+        <v>-0.06764729105837919</v>
       </c>
       <c r="J17" t="n">
         <v>-0.0101713811004291</v>
@@ -1091,7 +1103,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>38838</v>
       </c>
       <c r="B18" t="n">
@@ -1113,10 +1125,10 @@
         <v>70.44210526316</v>
       </c>
       <c r="H18" t="n">
-        <v>201.3</v>
+        <v>66.84</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.050005162139542</v>
+        <v>0.05248946677901056</v>
       </c>
       <c r="J18" t="n">
         <v>-0.0693822297032733</v>
@@ -1129,7 +1141,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>38869</v>
       </c>
       <c r="B19" t="n">
@@ -1151,10 +1163,10 @@
         <v>70.18727272727</v>
       </c>
       <c r="H19" t="n">
-        <v>201.8</v>
+        <v>67.16</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.056110113505947</v>
+        <v>0.0440891622042221</v>
       </c>
       <c r="J19" t="n">
         <v>-0.1109144688905292</v>
@@ -1167,7 +1179,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>38899</v>
       </c>
       <c r="B20" t="n">
@@ -1189,10 +1201,10 @@
         <v>68.85772727273</v>
       </c>
       <c r="H20" t="n">
-        <v>202.9</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0806707945092</v>
+        <v>0.02213954946619534</v>
       </c>
       <c r="J20" t="n">
         <v>0.0442081987437292</v>
@@ -1205,7 +1217,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>38930</v>
       </c>
       <c r="B21" t="n">
@@ -1227,10 +1239,10 @@
         <v>73.89714285714</v>
       </c>
       <c r="H21" t="n">
-        <v>203.8</v>
+        <v>67.8</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.014464955866853</v>
+        <v>0.08611196997542159</v>
       </c>
       <c r="J21" t="n">
         <v>0.1199079242809597</v>
@@ -1243,7 +1255,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>38961</v>
       </c>
       <c r="B22" t="n">
@@ -1265,10 +1277,10 @@
         <v>73.61217391304</v>
       </c>
       <c r="H22" t="n">
-        <v>202.8</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.013409853233159</v>
+        <v>0.08033265528065847</v>
       </c>
       <c r="J22" t="n">
         <v>0.0237536626048298</v>
@@ -1281,7 +1293,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>38991</v>
       </c>
       <c r="B23" t="n">
@@ -1303,10 +1315,10 @@
         <v>62.7719047619</v>
       </c>
       <c r="H23" t="n">
-        <v>201.9</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.168264928350185</v>
+        <v>-0.07985303856976156</v>
       </c>
       <c r="J23" t="n">
         <v>0.0038017010583892</v>
@@ -1319,7 +1331,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39022</v>
       </c>
       <c r="B24" t="n">
@@ -1341,10 +1353,10 @@
         <v>58.38</v>
       </c>
       <c r="H24" t="n">
-        <v>202</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.241294331975237</v>
+        <v>-0.1551779012837882</v>
       </c>
       <c r="J24" t="n">
         <v>0.0264141525484875</v>
@@ -1357,7 +1369,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39052</v>
       </c>
       <c r="B25" t="n">
@@ -1379,10 +1391,10 @@
         <v>58.48318181818</v>
       </c>
       <c r="H25" t="n">
-        <v>203.1</v>
+        <v>68.61</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.244959245969304</v>
+        <v>-0.1596990740857649</v>
       </c>
       <c r="J25" t="n">
         <v>0.08608319744448679</v>
@@ -1395,7 +1407,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39083</v>
       </c>
       <c r="B26" t="n">
@@ -1417,10 +1429,10 @@
         <v>62.31473684211</v>
       </c>
       <c r="H26" t="n">
-        <v>203.437</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.183158430399547</v>
+        <v>-0.1040801138677425</v>
       </c>
       <c r="J26" t="n">
         <v>-0.0086151431428387</v>
@@ -1433,7 +1445,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39114</v>
       </c>
       <c r="B27" t="n">
@@ -1455,10 +1467,10 @@
         <v>54.29909090909</v>
       </c>
       <c r="H27" t="n">
-        <v>204.226</v>
+        <v>70.31</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.32471973898208</v>
+        <v>-0.2584065514170386</v>
       </c>
       <c r="J27" t="n">
         <v>0.0202934442527222</v>
@@ -1471,7 +1483,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39142</v>
       </c>
       <c r="B28" t="n">
@@ -1493,10 +1505,10 @@
         <v>57.757</v>
       </c>
       <c r="H28" t="n">
-        <v>205.288</v>
+        <v>71.09</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.268169317091791</v>
+        <v>-0.2077021257638725</v>
       </c>
       <c r="J28" t="n">
         <v>0.07341863961623039</v>
@@ -1509,7 +1521,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39173</v>
       </c>
       <c r="B29" t="n">
@@ -1531,10 +1543,10 @@
         <v>62.14363636364</v>
       </c>
       <c r="H29" t="n">
-        <v>205.904</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.197961619611542</v>
+        <v>-0.140388878920537</v>
       </c>
       <c r="J29" t="n">
         <v>0.0283826976092349</v>
@@ -1547,7 +1559,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39203</v>
       </c>
       <c r="B30" t="n">
@@ -1569,10 +1581,10 @@
         <v>67.39842105263</v>
       </c>
       <c r="H30" t="n">
-        <v>206.755</v>
+        <v>71.92</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.12091292628322</v>
+        <v>-0.0649327990383517</v>
       </c>
       <c r="J30" t="n">
         <v>-0.0616928797259426</v>
@@ -1585,7 +1597,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39234</v>
       </c>
       <c r="B31" t="n">
@@ -1607,10 +1619,10 @@
         <v>67.47608695652001</v>
       </c>
       <c r="H31" t="n">
-        <v>207.234</v>
+        <v>72.37</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.122075321787511</v>
+        <v>-0.0700185810778553</v>
       </c>
       <c r="J31" t="n">
         <v>0.042395207825411</v>
@@ -1623,7 +1635,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39264</v>
       </c>
       <c r="B32" t="n">
@@ -1645,10 +1657,10 @@
         <v>71.31619047619</v>
       </c>
       <c r="H32" t="n">
-        <v>207.603</v>
+        <v>73.06</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.068504225009455</v>
+        <v>-0.02415764432221845</v>
       </c>
       <c r="J32" t="n">
         <v>0.016590709679539</v>
@@ -1661,7 +1673,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39295</v>
       </c>
       <c r="B33" t="n">
@@ -1683,10 +1695,10 @@
         <v>77.20409090909</v>
       </c>
       <c r="H33" t="n">
-        <v>207.667</v>
+        <v>73.7</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9894833885773489</v>
+        <v>0.04644964748185121</v>
       </c>
       <c r="J33" t="n">
         <v>-0.0224826914683404</v>
@@ -1699,7 +1711,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39326</v>
       </c>
       <c r="B34" t="n">
@@ -1721,10 +1733,10 @@
         <v>70.79652173913</v>
       </c>
       <c r="H34" t="n">
-        <v>208.547</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.080354563985464</v>
+        <v>-0.04100670773387272</v>
       </c>
       <c r="J34" t="n">
         <v>-0.0304360230995399</v>
@@ -1737,7 +1749,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39356</v>
       </c>
       <c r="B35" t="n">
@@ -1759,10 +1771,10 @@
         <v>77.127</v>
       </c>
       <c r="H35" t="n">
-        <v>209.19</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9977895160830164</v>
+        <v>0.03666974091184905</v>
       </c>
       <c r="J35" t="n">
         <v>0.0334638762657544</v>
@@ -1775,7 +1787,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39387</v>
       </c>
       <c r="B36" t="n">
@@ -1797,10 +1809,10 @@
         <v>82.85782608696</v>
       </c>
       <c r="H36" t="n">
-        <v>210.834</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.933944893655644</v>
+        <v>0.09206682129562971</v>
       </c>
       <c r="J36" t="n">
         <v>-0.0146355869459497</v>
@@ -1813,7 +1825,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39417</v>
       </c>
       <c r="B37" t="n">
@@ -1835,10 +1847,10 @@
         <v>92.52818181818</v>
       </c>
       <c r="H37" t="n">
-        <v>211.445</v>
+        <v>76.5</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8264516509657867</v>
+        <v>0.1902225255885748</v>
       </c>
       <c r="J37" t="n">
         <v>0.0538421950580723</v>
@@ -1851,7 +1863,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39448</v>
       </c>
       <c r="B38" t="n">
@@ -1873,10 +1885,10 @@
         <v>91.45</v>
       </c>
       <c r="H38" t="n">
-        <v>212.174</v>
+        <v>77.36</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.8416143179171502</v>
+        <v>0.1673225236918361</v>
       </c>
       <c r="J38" t="n">
         <v>-0.08703196674539269</v>
@@ -1889,7 +1901,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39479</v>
       </c>
       <c r="B39" t="n">
@@ -1911,10 +1923,10 @@
         <v>91.92045454545</v>
       </c>
       <c r="H39" t="n">
-        <v>212.687</v>
+        <v>79.15000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8388980228517822</v>
+        <v>0.1495787922126759</v>
       </c>
       <c r="J39" t="n">
         <v>0.0201653006410733</v>
@@ -1927,7 +1939,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39508</v>
       </c>
       <c r="B40" t="n">
@@ -1949,10 +1961,10 @@
         <v>94.81666666667</v>
       </c>
       <c r="H40" t="n">
-        <v>213.448</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.8114480407556419</v>
+        <v>0.1686693484542685</v>
       </c>
       <c r="J40" t="n">
         <v>-0.0596381293296666</v>
@@ -1965,7 +1977,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39539</v>
       </c>
       <c r="B41" t="n">
@@ -1987,10 +1999,10 @@
         <v>103.2775</v>
       </c>
       <c r="H41" t="n">
-        <v>213.942</v>
+        <v>81.06</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7282854100461442</v>
+        <v>0.2422299190034254</v>
       </c>
       <c r="J41" t="n">
         <v>-0.0139503164959098</v>
@@ -2003,7 +2015,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39569</v>
       </c>
       <c r="B42" t="n">
@@ -2025,10 +2037,10 @@
         <v>110.18772727273</v>
       </c>
       <c r="H42" t="n">
-        <v>215.208</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.6694194795619621</v>
+        <v>0.292908573591852</v>
       </c>
       <c r="J42" t="n">
         <v>0.0626351232401791</v>
@@ -2041,7 +2053,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39600</v>
       </c>
       <c r="B43" t="n">
@@ -2063,10 +2075,10 @@
         <v>123.93619047619</v>
       </c>
       <c r="H43" t="n">
-        <v>217.463</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5622618808923203</v>
+        <v>0.3970782238299302</v>
       </c>
       <c r="J43" t="n">
         <v>-0.0379861256720843</v>
@@ -2079,7 +2091,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>39630</v>
       </c>
       <c r="B44" t="n">
@@ -2101,10 +2113,10 @@
         <v>133.04857142857</v>
       </c>
       <c r="H44" t="n">
-        <v>219.016</v>
+        <v>84.13</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.4984305262445385</v>
+        <v>0.4583510387012657</v>
       </c>
       <c r="J44" t="n">
         <v>-0.0835100929303038</v>
@@ -2117,7 +2129,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>39661</v>
       </c>
       <c r="B45" t="n">
@@ -2139,10 +2151,10 @@
         <v>133.87304347826</v>
       </c>
       <c r="H45" t="n">
-        <v>218.69</v>
+        <v>84.56</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4907632877805872</v>
+        <v>0.459430572557662</v>
       </c>
       <c r="J45" t="n">
         <v>-0.07376295237086961</v>
@@ -2155,7 +2167,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>39692</v>
       </c>
       <c r="B46" t="n">
@@ -2177,10 +2189,10 @@
         <v>113.84904761905</v>
       </c>
       <c r="H46" t="n">
-        <v>218.877</v>
+        <v>84.86</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6536365009508804</v>
+        <v>0.2938705874748448</v>
       </c>
       <c r="J46" t="n">
         <v>-0.1616185508460246</v>
@@ -2193,7 +2205,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>39722</v>
       </c>
       <c r="B47" t="n">
@@ -2215,10 +2227,10 @@
         <v>99.06409090909</v>
       </c>
       <c r="H47" t="n">
-        <v>216.995</v>
+        <v>85.54000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.7841072882075819</v>
+        <v>0.1467829207940019</v>
       </c>
       <c r="J47" t="n">
         <v>-0.5726598895588149</v>
@@ -2231,7 +2243,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>39753</v>
       </c>
       <c r="B48" t="n">
@@ -2253,10 +2265,10 @@
         <v>72.84260869565</v>
       </c>
       <c r="H48" t="n">
-        <v>213.153</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.073709149436024</v>
+        <v>-0.1697602526783752</v>
       </c>
       <c r="J48" t="n">
         <v>-0.1752824309361234</v>
@@ -2269,7 +2281,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>39783</v>
       </c>
       <c r="B49" t="n">
@@ -2291,10 +2303,10 @@
         <v>53.241</v>
       </c>
       <c r="H49" t="n">
-        <v>211.398</v>
+        <v>87.03</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.378913836432909</v>
+        <v>-0.4914241105808848</v>
       </c>
       <c r="J49" t="n">
         <v>-0.0328830615933606</v>
@@ -2307,7 +2319,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>39814</v>
       </c>
       <c r="B50" t="n">
@@ -2329,10 +2341,10 @@
         <v>41.58090909091</v>
       </c>
       <c r="H50" t="n">
-        <v>211.933</v>
+        <v>87.63</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.628629041136604</v>
+        <v>-0.7454822592186492</v>
       </c>
       <c r="J50" t="n">
         <v>0.0004445990949282</v>
@@ -2345,7 +2357,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>39845</v>
       </c>
       <c r="B51" t="n">
@@ -2367,10 +2379,10 @@
         <v>44.86</v>
       </c>
       <c r="H51" t="n">
-        <v>212.705</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.556359700125097</v>
+        <v>-0.6930357164791299</v>
       </c>
       <c r="J51" t="n">
         <v>0.1296016912505857</v>
@@ -2383,11 +2395,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>39873</v>
       </c>
       <c r="B52" t="n">
-        <v>13.2460749040845</v>
+        <v>13.24607490408451</v>
       </c>
       <c r="C52" t="n">
         <v>3.07402318029276</v>
@@ -2405,10 +2417,10 @@
         <v>43.2425</v>
       </c>
       <c r="H52" t="n">
-        <v>212.495</v>
+        <v>91.19</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.592094650739944</v>
+        <v>-0.7461214340096327</v>
       </c>
       <c r="J52" t="n">
         <v>0.1241994882454609</v>
@@ -2421,7 +2433,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>39904</v>
       </c>
       <c r="B53" t="n">
@@ -2443,10 +2455,10 @@
         <v>46.83909090909</v>
       </c>
       <c r="H53" t="n">
-        <v>212.709</v>
+        <v>92.39</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.513206904317955</v>
+        <v>-0.6793006175725256</v>
       </c>
       <c r="J53" t="n">
         <v>0.3614108367597115</v>
@@ -2459,7 +2471,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>39934</v>
       </c>
       <c r="B54" t="n">
@@ -2481,10 +2493,10 @@
         <v>50.84523809524</v>
       </c>
       <c r="H54" t="n">
-        <v>213.022</v>
+        <v>93.02</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.43260897476254</v>
+        <v>-0.6040280517977603</v>
       </c>
       <c r="J54" t="n">
         <v>0.1520966269082375</v>
@@ -2497,11 +2509,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>39965</v>
       </c>
       <c r="B55" t="n">
-        <v>-15.08860714692284</v>
+        <v>-15.08860714692285</v>
       </c>
       <c r="C55" t="n">
         <v>3.430754526529753</v>
@@ -2519,10 +2531,10 @@
         <v>57.94095238095</v>
       </c>
       <c r="H55" t="n">
-        <v>214.79</v>
+        <v>93.55</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.310236377044681</v>
+        <v>-0.4790716231486085</v>
       </c>
       <c r="J55" t="n">
         <v>-0.0126045070650793</v>
@@ -2535,7 +2547,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>39995</v>
       </c>
       <c r="B56" t="n">
@@ -2557,10 +2569,10 @@
         <v>68.61681818181999</v>
       </c>
       <c r="H56" t="n">
-        <v>214.726</v>
+        <v>94.12</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.140825129076423</v>
+        <v>-0.3160328961745682</v>
       </c>
       <c r="J56" t="n">
         <v>0.0277821156965591</v>
@@ -2573,7 +2585,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40026</v>
       </c>
       <c r="B57" t="n">
@@ -2595,10 +2607,10 @@
         <v>64.91</v>
       </c>
       <c r="H57" t="n">
-        <v>215.445</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.199703961506518</v>
+        <v>-0.3778178961926333</v>
       </c>
       <c r="J57" t="n">
         <v>0.108044303923112</v>
@@ -2611,7 +2623,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40057</v>
       </c>
       <c r="B58" t="n">
@@ -2633,10 +2645,10 @@
         <v>72.50476190476</v>
       </c>
       <c r="H58" t="n">
-        <v>215.861</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.090982440870069</v>
+        <v>-0.2671673500893474</v>
       </c>
       <c r="J58" t="n">
         <v>0.1482282471802127</v>
@@ -2649,7 +2661,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40087</v>
       </c>
       <c r="B59" t="n">
@@ -2671,10 +2683,10 @@
         <v>67.68681818182</v>
       </c>
       <c r="H59" t="n">
-        <v>216.509</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.162740665336278</v>
+        <v>-0.3356113329647439</v>
       </c>
       <c r="J59" t="n">
         <v>-0.0191895960770027</v>
@@ -2687,7 +2699,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40118</v>
       </c>
       <c r="B60" t="n">
@@ -2709,10 +2721,10 @@
         <v>73.19409090908999</v>
       </c>
       <c r="H60" t="n">
-        <v>217.234</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.087860421139099</v>
+        <v>-0.2573880922226337</v>
       </c>
       <c r="J60" t="n">
         <v>0.07272932575195939</v>
@@ -2725,7 +2737,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40148</v>
       </c>
       <c r="B61" t="n">
@@ -2747,10 +2759,10 @@
         <v>77.03666666667</v>
       </c>
       <c r="H61" t="n">
-        <v>217.347</v>
+        <v>94.95</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.037213655729833</v>
+        <v>-0.2090689382710824</v>
       </c>
       <c r="J61" t="n">
         <v>0.0700444824826487</v>
@@ -2763,7 +2775,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40179</v>
       </c>
       <c r="B62" t="n">
@@ -2785,10 +2797,10 @@
         <v>74.66954545455</v>
       </c>
       <c r="H62" t="n">
-        <v>217.488</v>
+        <v>95.34</v>
       </c>
       <c r="I62" t="n">
-        <v>-1.069071358954329</v>
+        <v>-0.2443771321381165</v>
       </c>
       <c r="J62" t="n">
         <v>0.0714520859773166</v>
@@ -2801,7 +2813,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40210</v>
       </c>
       <c r="B63" t="n">
@@ -2823,10 +2835,10 @@
         <v>76.373</v>
       </c>
       <c r="H63" t="n">
-        <v>217.281</v>
+        <v>96.91</v>
       </c>
       <c r="I63" t="n">
-        <v>-1.04556221614664</v>
+        <v>-0.2381534821769522</v>
       </c>
       <c r="J63" t="n">
         <v>0.06284550412308219</v>
@@ -2839,7 +2851,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40238</v>
       </c>
       <c r="B64" t="n">
@@ -2861,10 +2873,10 @@
         <v>74.312</v>
       </c>
       <c r="H64" t="n">
-        <v>217.353</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>-1.073250313876824</v>
+        <v>-0.2740384457567888</v>
       </c>
       <c r="J64" t="n">
         <v>0.1057953519129029</v>
@@ -2877,7 +2889,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40269</v>
       </c>
       <c r="B65" t="n">
@@ -2899,10 +2911,10 @@
         <v>79.27478260869999</v>
       </c>
       <c r="H65" t="n">
-        <v>217.403</v>
+        <v>98.36</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.008832695862094</v>
+        <v>-0.2157141391701662</v>
       </c>
       <c r="J65" t="n">
         <v>-0.0066469673443663</v>
@@ -2915,7 +2927,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40299</v>
       </c>
       <c r="B66" t="n">
@@ -2937,10 +2949,10 @@
         <v>84.97857142857001</v>
       </c>
       <c r="H66" t="n">
-        <v>217.29</v>
+        <v>98.64</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.9388337430081393</v>
+        <v>-0.1490777349888832</v>
       </c>
       <c r="J66" t="n">
         <v>-0.0865161622608656</v>
@@ -2953,7 +2965,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40330</v>
       </c>
       <c r="B67" t="n">
@@ -2975,10 +2987,10 @@
         <v>76.25095238095</v>
       </c>
       <c r="H67" t="n">
-        <v>217.199</v>
+        <v>99.14</v>
       </c>
       <c r="I67" t="n">
-        <v>-1.046784078346131</v>
+        <v>-0.2625030869409422</v>
       </c>
       <c r="J67" t="n">
         <v>0.0176740342626207</v>
@@ -2991,7 +3003,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40360</v>
       </c>
       <c r="B68" t="n">
@@ -3013,10 +3025,10 @@
         <v>74.83818181818</v>
       </c>
       <c r="H68" t="n">
-        <v>217.605</v>
+        <v>99.52</v>
       </c>
       <c r="I68" t="n">
-        <v>-1.0673532858002</v>
+        <v>-0.2850304221320945</v>
       </c>
       <c r="J68" t="n">
         <v>0.0507662339373116</v>
@@ -3029,7 +3041,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40391</v>
       </c>
       <c r="B69" t="n">
@@ -3051,10 +3063,10 @@
         <v>74.73545454545</v>
       </c>
       <c r="H69" t="n">
-        <v>217.923</v>
+        <v>99.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-1.070187184070859</v>
+        <v>-0.2900148600962176</v>
       </c>
       <c r="J69" t="n">
         <v>0.0079698907253629</v>
@@ -3067,7 +3079,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40422</v>
       </c>
       <c r="B70" t="n">
@@ -3089,10 +3101,10 @@
         <v>76.69318181817999</v>
       </c>
       <c r="H70" t="n">
-        <v>218.275</v>
+        <v>100.43</v>
       </c>
       <c r="I70" t="n">
-        <v>-1.045942925431695</v>
+        <v>-0.2696481571400717</v>
       </c>
       <c r="J70" t="n">
         <v>0.0878095532275882</v>
@@ -3105,7 +3117,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40452</v>
       </c>
       <c r="B71" t="n">
@@ -3127,10 +3139,10 @@
         <v>77.78681818182</v>
       </c>
       <c r="H71" t="n">
-        <v>219.035</v>
+        <v>101.27</v>
       </c>
       <c r="I71" t="n">
-        <v>-1.035259549679845</v>
+        <v>-0.263818232625372</v>
       </c>
       <c r="J71" t="n">
         <v>0.1072718357480084</v>
@@ -3143,7 +3155,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40483</v>
       </c>
       <c r="B72" t="n">
@@ -3165,10 +3177,10 @@
         <v>82.91809523809999</v>
       </c>
       <c r="H72" t="n">
-        <v>219.59</v>
+        <v>101.78</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.973908855033514</v>
+        <v>-0.2049603049363</v>
       </c>
       <c r="J72" t="n">
         <v>0.06870153222403449</v>
@@ -3181,7 +3193,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40513</v>
       </c>
       <c r="B73" t="n">
@@ -3203,10 +3215,10 @@
         <v>85.67</v>
       </c>
       <c r="H73" t="n">
-        <v>220.472</v>
+        <v>102.6</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.9452679967207969</v>
+        <v>-0.1803352267607163</v>
       </c>
       <c r="J73" t="n">
         <v>0.1291250780299986</v>
@@ -3219,7 +3231,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40544</v>
       </c>
       <c r="B74" t="n">
@@ -3241,10 +3253,10 @@
         <v>91.79652173913</v>
       </c>
       <c r="H74" t="n">
-        <v>221.187</v>
+        <v>103.71</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.879434090220899</v>
+        <v>-0.1220241352449865</v>
       </c>
       <c r="J74" t="n">
         <v>-0.008029881836804901</v>
@@ -3257,7 +3269,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="B75" t="n">
@@ -3279,10 +3291,10 @@
         <v>96.29428571429</v>
       </c>
       <c r="H75" t="n">
-        <v>221.898</v>
+        <v>106.17</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.8348088381625427</v>
+        <v>-0.09763260435904364</v>
       </c>
       <c r="J75" t="n">
         <v>-0.0137226576203008</v>
@@ -3295,7 +3307,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40603</v>
       </c>
       <c r="B76" t="n">
@@ -3317,10 +3329,10 @@
         <v>103.9555</v>
       </c>
       <c r="H76" t="n">
-        <v>223.046</v>
+        <v>107</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.7634151052573932</v>
+        <v>-0.02886591150466167</v>
       </c>
       <c r="J76" t="n">
         <v>-0.0386519079699212</v>
@@ -3333,7 +3345,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>40634</v>
       </c>
       <c r="B77" t="n">
@@ -3355,10 +3367,10 @@
         <v>114.44130434783</v>
       </c>
       <c r="H77" t="n">
-        <v>224.093</v>
+        <v>107.66</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.6719990784900602</v>
+        <v>0.06108395264082134</v>
       </c>
       <c r="J77" t="n">
         <v>-0.0588413930208506</v>
@@ -3371,7 +3383,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>40664</v>
       </c>
       <c r="B78" t="n">
@@ -3393,10 +3405,10 @@
         <v>123.07</v>
       </c>
       <c r="H78" t="n">
-        <v>224.806</v>
+        <v>108.12</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.6024845088705675</v>
+        <v>0.1295115777759985</v>
       </c>
       <c r="J78" t="n">
         <v>-0.0108285021591783</v>
@@ -3409,7 +3421,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>40695</v>
       </c>
       <c r="B79" t="n">
@@ -3431,10 +3443,10 @@
         <v>114.45818181818</v>
       </c>
       <c r="H79" t="n">
-        <v>224.806</v>
+        <v>108.64</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.6750282760665263</v>
+        <v>0.05216986817790037</v>
       </c>
       <c r="J79" t="n">
         <v>-0.0169156126886722</v>
@@ -3447,7 +3459,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>40725</v>
       </c>
       <c r="B80" t="n">
@@ -3469,10 +3481,10 @@
         <v>113.75772727273</v>
       </c>
       <c r="H80" t="n">
-        <v>225.395</v>
+        <v>108.89</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6837834309817392</v>
+        <v>0.04373278923376756</v>
       </c>
       <c r="J80" t="n">
         <v>0.0238314412099249</v>
@@ -3485,7 +3497,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="B81" t="n">
@@ -3507,10 +3519,10 @@
         <v>116.46</v>
       </c>
       <c r="H81" t="n">
-        <v>226.106</v>
+        <v>108.88</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6634560494534139</v>
+        <v>0.06730150806576329</v>
       </c>
       <c r="J81" t="n">
         <v>-0.1540611657548005</v>
@@ -3523,7 +3535,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>40787</v>
       </c>
       <c r="B82" t="n">
@@ -3545,10 +3557,10 @@
         <v>110.08130434783</v>
       </c>
       <c r="H82" t="n">
-        <v>226.597</v>
+        <v>108.62</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.721953886113412</v>
+        <v>0.01336367059816013</v>
       </c>
       <c r="J82" t="n">
         <v>-0.0683028670225152</v>
@@ -3561,11 +3573,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>40817</v>
       </c>
       <c r="B83" t="n">
-        <v>9.26176652574722</v>
+        <v>9.261766525747221</v>
       </c>
       <c r="C83" t="n">
         <v>3.806196866255272</v>
@@ -3583,10 +3595,10 @@
         <v>110.87909090909</v>
       </c>
       <c r="H83" t="n">
-        <v>226.75</v>
+        <v>108.58</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.7154077524591074</v>
+        <v>0.02095310805883432</v>
       </c>
       <c r="J83" t="n">
         <v>0.0538524348636091</v>
@@ -3599,7 +3611,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>40848</v>
       </c>
       <c r="B84" t="n">
@@ -3621,10 +3633,10 @@
         <v>109.46857142857</v>
       </c>
       <c r="H84" t="n">
-        <v>227.169</v>
+        <v>109.1</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.730056744734167</v>
+        <v>0.003372596302549269</v>
       </c>
       <c r="J84" t="n">
         <v>-0.0334112885843662</v>
@@ -3637,7 +3649,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>40878</v>
       </c>
       <c r="B85" t="n">
@@ -3659,10 +3671,10 @@
         <v>110.50409090909</v>
       </c>
       <c r="H85" t="n">
-        <v>227.223</v>
+        <v>109.56</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.7208793720434725</v>
+        <v>0.008580197679360246</v>
       </c>
       <c r="J85" t="n">
         <v>-0.124810844201022</v>
@@ -3675,7 +3687,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>40909</v>
       </c>
       <c r="B86" t="n">
@@ -3697,10 +3709,10 @@
         <v>107.90904761905</v>
       </c>
       <c r="H86" t="n">
-        <v>227.842</v>
+        <v>110.04</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7473636856351531</v>
+        <v>-0.01955521541655525</v>
       </c>
       <c r="J86" t="n">
         <v>0.115087353774717</v>
@@ -3713,7 +3725,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>40940</v>
       </c>
       <c r="B87" t="n">
@@ -3735,10 +3747,10 @@
         <v>111.15619047619</v>
       </c>
       <c r="H87" t="n">
-        <v>228.329</v>
+        <v>110.59</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.7198512376599986</v>
+        <v>0.005106664564571872</v>
       </c>
       <c r="J87" t="n">
         <v>0.1281066643934387</v>
@@ -3751,7 +3763,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>40969</v>
       </c>
       <c r="B88" t="n">
@@ -3773,10 +3785,10 @@
         <v>119.70238095238</v>
       </c>
       <c r="H88" t="n">
-        <v>228.807</v>
+        <v>111</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.6478703500798071</v>
+        <v>0.07547830205109651</v>
       </c>
       <c r="J88" t="n">
         <v>-0.0190273965309391</v>
@@ -3789,11 +3801,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41000</v>
       </c>
       <c r="B89" t="n">
-        <v>-3.768373197178725</v>
+        <v>-3.768373197178724</v>
       </c>
       <c r="C89" t="n">
         <v>3.857750690414038</v>
@@ -3811,10 +3823,10 @@
         <v>124.92863636364</v>
       </c>
       <c r="H89" t="n">
-        <v>229.187</v>
+        <v>111.64</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.6067955990285396</v>
+        <v>0.1124632565126511</v>
       </c>
       <c r="J89" t="n">
         <v>0.0078549526613933</v>
@@ -3827,7 +3839,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41030</v>
       </c>
       <c r="B90" t="n">
@@ -3849,10 +3861,10 @@
         <v>120.4635</v>
       </c>
       <c r="H90" t="n">
-        <v>228.713</v>
+        <v>111.99</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.6411211399574892</v>
+        <v>0.07293722088693855</v>
       </c>
       <c r="J90" t="n">
         <v>-0.1351539536818347</v>
@@ -3865,7 +3877,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41061</v>
       </c>
       <c r="B91" t="n">
@@ -3887,10 +3899,10 @@
         <v>110.52173913044</v>
       </c>
       <c r="H91" t="n">
-        <v>228.524</v>
+        <v>112.57</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.7264290018211588</v>
+        <v>-0.01836301454641553</v>
       </c>
       <c r="J91" t="n">
         <v>0.0256955285595097</v>
@@ -3903,7 +3915,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41091</v>
       </c>
       <c r="B92" t="n">
@@ -3925,10 +3937,10 @@
         <v>95.58904761905001</v>
       </c>
       <c r="H92" t="n">
-        <v>228.59</v>
+        <v>113.57</v>
       </c>
       <c r="I92" t="n">
-        <v>-0.8718717570319212</v>
+        <v>-0.1723611380635193</v>
       </c>
       <c r="J92" t="n">
         <v>0.0541406135446269</v>
@@ -3941,11 +3953,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41122</v>
       </c>
       <c r="B93" t="n">
-        <v>-0.1021760088819951</v>
+        <v>-0.1021760088819952</v>
       </c>
       <c r="C93" t="n">
         <v>3.742570727008806</v>
@@ -3963,10 +3975,10 @@
         <v>103.14090909091</v>
       </c>
       <c r="H93" t="n">
-        <v>229.918</v>
+        <v>114.97</v>
       </c>
       <c r="I93" t="n">
-        <v>-0.8016266208861627</v>
+        <v>-0.1085751220367319</v>
       </c>
       <c r="J93" t="n">
         <v>0.0434197253430603</v>
@@ -3979,7 +3991,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41153</v>
       </c>
       <c r="B94" t="n">
@@ -4001,10 +4013,10 @@
         <v>113.34</v>
       </c>
       <c r="H94" t="n">
-        <v>231.015</v>
+        <v>115.08</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.7120904927370653</v>
+        <v>-0.01523538794187473</v>
       </c>
       <c r="J94" t="n">
         <v>-0.0455923184737763</v>
@@ -4017,7 +4029,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41183</v>
       </c>
       <c r="B95" t="n">
@@ -4039,10 +4051,10 @@
         <v>113.3825</v>
       </c>
       <c r="H95" t="n">
-        <v>231.638</v>
+        <v>115.72</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.7144087498356493</v>
+        <v>-0.02040642171064544</v>
       </c>
       <c r="J95" t="n">
         <v>-0.0110603671502502</v>
@@ -4055,7 +4067,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41214</v>
       </c>
       <c r="B96" t="n">
@@ -4077,10 +4089,10 @@
         <v>111.97347826087</v>
       </c>
       <c r="H96" t="n">
-        <v>231.249</v>
+        <v>116.25</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.7252330100478392</v>
+        <v>-0.03748100245644448</v>
       </c>
       <c r="J96" t="n">
         <v>0.014688017180962</v>
@@ -4093,7 +4105,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41244</v>
       </c>
       <c r="B97" t="n">
@@ -4115,10 +4127,10 @@
         <v>109.71181818182</v>
       </c>
       <c r="H97" t="n">
-        <v>231.221</v>
+        <v>116.64</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.7455168698140575</v>
+        <v>-0.06123517495119124</v>
       </c>
       <c r="J97" t="n">
         <v>0.0629844102035193</v>
@@ -4131,7 +4143,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41275</v>
       </c>
       <c r="B98" t="n">
@@ -4153,10 +4165,10 @@
         <v>109.6765</v>
       </c>
       <c r="H98" t="n">
-        <v>231.679</v>
+        <v>117.27</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.7478176691586604</v>
+        <v>-0.06694384474193971</v>
       </c>
       <c r="J98" t="n">
         <v>0.09261829600554521</v>
@@ -4169,7 +4181,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41306</v>
       </c>
       <c r="B99" t="n">
@@ -4191,10 +4203,10 @@
         <v>112.97363636364</v>
       </c>
       <c r="H99" t="n">
-        <v>232.937</v>
+        <v>118.41</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.7236135457629675</v>
+        <v>-0.04699869336718354</v>
       </c>
       <c r="J99" t="n">
         <v>0.0390595540822324</v>
@@ -4207,7 +4219,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41334</v>
       </c>
       <c r="B100" t="n">
@@ -4229,10 +4241,10 @@
         <v>116.5195</v>
       </c>
       <c r="H100" t="n">
-        <v>232.282</v>
+        <v>119.08</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.6898935097914922</v>
+        <v>-0.02173689517437083</v>
       </c>
       <c r="J100" t="n">
         <v>-0.0211872256708396</v>
@@ -4245,7 +4257,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41365</v>
       </c>
       <c r="B101" t="n">
@@ -4267,10 +4279,10 @@
         <v>109.24</v>
       </c>
       <c r="H101" t="n">
-        <v>231.797</v>
+        <v>119.48</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7523146920248518</v>
+        <v>-0.08960169674240515</v>
       </c>
       <c r="J101" t="n">
         <v>-0.005287154308375</v>
@@ -4283,7 +4295,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41395</v>
       </c>
       <c r="B102" t="n">
@@ -4305,10 +4317,10 @@
         <v>102.87545454546</v>
       </c>
       <c r="H102" t="n">
-        <v>231.893</v>
+        <v>120.09</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.8127569809687873</v>
+        <v>-0.1547223842602348</v>
       </c>
       <c r="J102" t="n">
         <v>0.0262857640931439</v>
@@ -4321,11 +4333,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41426</v>
       </c>
       <c r="B103" t="n">
-        <v>-2.126261964223034</v>
+        <v>-2.126261964223033</v>
       </c>
       <c r="C103" t="n">
         <v>3.73297856993634</v>
@@ -4343,10 +4355,10 @@
         <v>103.02695652174</v>
       </c>
       <c r="H103" t="n">
-        <v>232.445</v>
+        <v>120.88</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.8136629701112463</v>
+        <v>-0.1598076501726311</v>
       </c>
       <c r="J103" t="n">
         <v>0.0194279514445749</v>
@@ -4359,7 +4371,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41456</v>
       </c>
       <c r="B104" t="n">
@@ -4381,10 +4393,10 @@
         <v>103.11</v>
       </c>
       <c r="H104" t="n">
-        <v>232.9</v>
+        <v>121.39</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.8148127973604433</v>
+        <v>-0.1632121233798607</v>
       </c>
       <c r="J104" t="n">
         <v>-0.004767860093505</v>
@@ -4397,7 +4409,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41487</v>
       </c>
       <c r="B105" t="n">
@@ -4419,10 +4431,10 @@
         <v>107.71608695652</v>
       </c>
       <c r="H105" t="n">
-        <v>233.456</v>
+        <v>122.39</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.7734946813008312</v>
+        <v>-0.127713726173412</v>
       </c>
       <c r="J105" t="n">
         <v>-0.0136028914576993</v>
@@ -4435,7 +4447,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41518</v>
       </c>
       <c r="B106" t="n">
@@ -4457,10 +4469,10 @@
         <v>110.96454545455</v>
       </c>
       <c r="H106" t="n">
-        <v>233.544</v>
+        <v>122.56</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.744159756217174</v>
+        <v>-0.09938996602165684</v>
       </c>
       <c r="J106" t="n">
         <v>0.0142906159504292</v>
@@ -4473,7 +4485,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41548</v>
       </c>
       <c r="B107" t="n">
@@ -4495,10 +4507,10 @@
         <v>111.62142857143</v>
       </c>
       <c r="H107" t="n">
-        <v>233.669</v>
+        <v>122.81</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.7387925402472781</v>
+        <v>-0.09552540181828295</v>
       </c>
       <c r="J107" t="n">
         <v>0.0413744711715509</v>
@@ -4511,7 +4523,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41579</v>
       </c>
       <c r="B108" t="n">
@@ -4533,10 +4545,10 @@
         <v>109.47869565217</v>
       </c>
       <c r="H108" t="n">
-        <v>234.1</v>
+        <v>123.51</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.760018404423767</v>
+        <v>-0.1205921543768245</v>
       </c>
       <c r="J108" t="n">
         <v>0.0273695310775377</v>
@@ -4549,7 +4561,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>41609</v>
       </c>
       <c r="B109" t="n">
@@ -4571,10 +4583,10 @@
         <v>108.07619047619</v>
       </c>
       <c r="H109" t="n">
-        <v>234.719</v>
+        <v>124.21</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.7755526082190167</v>
+        <v>-0.1391372357848875</v>
       </c>
       <c r="J109" t="n">
         <v>0.012234415788269</v>
@@ -4587,7 +4599,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>41640</v>
       </c>
       <c r="B110" t="n">
@@ -4609,10 +4621,10 @@
         <v>110.674</v>
       </c>
       <c r="H110" t="n">
-        <v>235.288</v>
+        <v>124.84</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.7542213525946186</v>
+        <v>-0.1204439742893912</v>
       </c>
       <c r="J110" t="n">
         <v>-0.1012002578588049</v>
@@ -4625,7 +4637,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>41671</v>
       </c>
       <c r="B111" t="n">
@@ -4647,10 +4659,10 @@
         <v>107.42</v>
       </c>
       <c r="H111" t="n">
-        <v>235.547</v>
+        <v>125.58</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.7851640844381933</v>
+        <v>-0.1561966212086494</v>
       </c>
       <c r="J111" t="n">
         <v>-0.0191031825165737</v>
@@ -4663,7 +4675,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>41699</v>
       </c>
       <c r="B112" t="n">
@@ -4685,10 +4697,10 @@
         <v>108.81</v>
       </c>
       <c r="H112" t="n">
-        <v>236.028</v>
+        <v>126.45</v>
       </c>
       <c r="I112" t="n">
-        <v>-0.7743472000928353</v>
+        <v>-0.1502437311530533</v>
       </c>
       <c r="J112" t="n">
         <v>-0.0336289884949643</v>
@@ -4701,7 +4713,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>41730</v>
       </c>
       <c r="B113" t="n">
@@ -4723,10 +4735,10 @@
         <v>107.4</v>
       </c>
       <c r="H113" t="n">
-        <v>236.468</v>
+        <v>127.74</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.7892527101485545</v>
+        <v>-0.1734367660586784</v>
       </c>
       <c r="J113" t="n">
         <v>0.0043120141499422</v>
@@ -4739,7 +4751,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>41760</v>
       </c>
       <c r="B114" t="n">
@@ -4761,10 +4773,10 @@
         <v>107.79</v>
       </c>
       <c r="H114" t="n">
-        <v>236.918</v>
+        <v>128.89</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.7875291999115221</v>
+        <v>-0.1787744376231508</v>
       </c>
       <c r="J114" t="n">
         <v>0.0813694631709989</v>
@@ -4777,7 +4789,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>41791</v>
       </c>
       <c r="B115" t="n">
@@ -4799,10 +4811,10 @@
         <v>109.68</v>
       </c>
       <c r="H115" t="n">
-        <v>237.231</v>
+        <v>130.05</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.7714673147297972</v>
+        <v>-0.1703519566406024</v>
       </c>
       <c r="J115" t="n">
         <v>0.0558479640172482</v>
@@ -4815,7 +4827,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>41821</v>
       </c>
       <c r="B116" t="n">
@@ -4837,10 +4849,10 @@
         <v>111.87</v>
       </c>
       <c r="H116" t="n">
-        <v>237.498</v>
+        <v>130.86</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.752821719527768</v>
+        <v>-0.156790566582754</v>
       </c>
       <c r="J116" t="n">
         <v>-0.0278424661802016</v>
@@ -4853,7 +4865,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>41852</v>
       </c>
       <c r="B117" t="n">
@@ -4875,10 +4887,10 @@
         <v>106.98</v>
       </c>
       <c r="H117" t="n">
-        <v>237.46</v>
+        <v>131.5</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.7973572871345427</v>
+        <v>-0.2063649505147156</v>
       </c>
       <c r="J117" t="n">
         <v>-0.017907321897022</v>
@@ -4891,7 +4903,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>41883</v>
       </c>
       <c r="B118" t="n">
@@ -4913,10 +4925,10 @@
         <v>101.92</v>
       </c>
       <c r="H118" t="n">
-        <v>237.477</v>
+        <v>131.82</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.8458825848560805</v>
+        <v>-0.2572491638007204</v>
       </c>
       <c r="J118" t="n">
         <v>0.0479018047831214</v>
@@ -4929,7 +4941,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>41913</v>
       </c>
       <c r="B119" t="n">
@@ -4951,10 +4963,10 @@
         <v>97.34</v>
       </c>
       <c r="H119" t="n">
-        <v>237.43</v>
+        <v>132.67</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.8916628387838426</v>
+        <v>-0.3096548375235173</v>
       </c>
       <c r="J119" t="n">
         <v>0.0322347502559026</v>
@@ -4967,7 +4979,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>41944</v>
       </c>
       <c r="B120" t="n">
@@ -4989,10 +5001,10 @@
         <v>87.27</v>
       </c>
       <c r="H120" t="n">
-        <v>236.983</v>
+        <v>133.76</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.9989816474293889</v>
+        <v>-0.4270403881611715</v>
       </c>
       <c r="J120" t="n">
         <v>0.0160157051466871</v>
@@ -5005,7 +5017,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>41974</v>
       </c>
       <c r="B121" t="n">
@@ -5027,10 +5039,10 @@
         <v>78.44</v>
       </c>
       <c r="H121" t="n">
-        <v>236.252</v>
+        <v>135.47</v>
       </c>
       <c r="I121" t="n">
-        <v>-1.102565030618339</v>
+        <v>-0.5464162122645</v>
       </c>
       <c r="J121" t="n">
         <v>-0.1723685705659949</v>
